--- a/output/topology_excel/9875.xlsx
+++ b/output/topology_excel/9875.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,7 +652,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F10" t="n">
         <v>16</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
         <v>16</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F14" t="n">
         <v>16</v>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F15" t="n">
         <v>16</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F16" t="n">
         <v>16</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" t="n">
         <v>16</v>
@@ -814,10 +814,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
         <v>16</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20" t="n">
         <v>16</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" t="n">
         <v>16</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" t="n">
         <v>16</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F25" t="n">
         <v>16</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" t="n">
         <v>16</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B27" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F27" t="n">
         <v>16</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B29" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F29" t="n">
         <v>16</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B30" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F30" t="n">
         <v>16</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="B31" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" t="n">
         <v>16</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B32" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B33" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F33" t="n">
         <v>16</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B34" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B35" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B36" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B37" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F37" t="n">
         <v>16</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="B38" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F38" t="n">
         <v>16</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B39" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F39" t="n">
         <v>16</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="B40" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F40" t="n">
         <v>16</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="B41" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
         <v>16</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F42" t="n">
         <v>16</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B43" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="F43" t="n">
         <v>16</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B44" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F44" t="n">
         <v>16</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B45" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="F45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B46" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B47" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F47" t="n">
         <v>16</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F48" t="n">
         <v>16</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B49" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F49" t="n">
         <v>16</v>
@@ -1518,10 +1518,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="B50" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>247</v>
+        <v>81</v>
       </c>
       <c r="F50" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="B51" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F51" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="B52" t="n">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F52" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="B53" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,18 +1598,18 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B54" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1620,18 +1620,18 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="B55" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1642,18 +1642,18 @@
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F55" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="B56" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1664,18 +1664,18 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B57" t="n">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1686,18 +1686,18 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F57" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B58" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="F58" t="n">
         <v>19</v>
@@ -1716,10 +1716,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="B59" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F59" t="n">
         <v>19</v>
@@ -1738,10 +1738,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B60" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
         <v>19</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="B61" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1777,15 +1777,15 @@
         <v>70</v>
       </c>
       <c r="F61" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B62" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1796,18 +1796,18 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F62" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="B63" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F63" t="n">
         <v>19</v>
@@ -1826,87 +1826,87 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="F64" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B65" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>229</v>
+        <v>70</v>
       </c>
       <c r="F65" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="B66" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>171</v>
+        <v>75</v>
       </c>
       <c r="F66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B67" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>651</v>
+        <v>72</v>
       </c>
       <c r="F67" t="n">
         <v>19</v>
@@ -1914,21 +1914,21 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D68" t="n">
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>71</v>
       </c>
       <c r="F68" t="n">
         <v>19</v>
@@ -1936,76 +1936,76 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="B69" t="n">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="F69" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="F70" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="B71" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="F71" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2016,18 +2016,18 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>544</v>
+        <v>112</v>
       </c>
       <c r="F72" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B73" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2038,18 +2038,18 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>229</v>
+        <v>112</v>
       </c>
       <c r="F73" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B74" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F74" t="n">
         <v>16</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B75" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2082,15 +2082,15 @@
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>622</v>
+        <v>112</v>
       </c>
       <c r="F75" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B76" t="n">
         <v>6</v>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="F76" t="n">
         <v>16</v>
@@ -2112,10 +2112,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>228</v>
+        <v>113</v>
       </c>
       <c r="F77" t="n">
         <v>16</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B78" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2148,18 +2148,18 @@
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="F78" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B79" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2170,18 +2170,18 @@
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>622</v>
+        <v>159</v>
       </c>
       <c r="F79" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B80" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2195,15 +2195,15 @@
         <v>113</v>
       </c>
       <c r="F80" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B81" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F81" t="n">
         <v>16</v>
@@ -2222,10 +2222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B82" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="F82" t="n">
         <v>16</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B83" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2258,18 +2258,18 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="F83" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B84" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>228</v>
+        <v>122</v>
       </c>
       <c r="F84" t="n">
         <v>16</v>
@@ -2288,10 +2288,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B85" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F85" t="n">
         <v>16</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B86" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2324,18 +2324,18 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>652</v>
+        <v>90</v>
       </c>
       <c r="F86" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2346,18 +2346,18 @@
         <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>394</v>
+        <v>123</v>
       </c>
       <c r="F87" t="n">
-        <v>255</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B88" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>69</v>
+        <v>160</v>
       </c>
       <c r="F88" t="n">
         <v>16</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B89" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="F89" t="n">
         <v>16</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B90" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2412,18 +2412,18 @@
         <v>1</v>
       </c>
       <c r="E90" t="n">
-        <v>668</v>
+        <v>228</v>
       </c>
       <c r="F90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B91" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>378</v>
+        <v>123</v>
       </c>
       <c r="F91" t="n">
         <v>16</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B92" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2456,18 +2456,18 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>378</v>
+        <v>159</v>
       </c>
       <c r="F92" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B93" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="E93" t="n">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="F93" t="n">
         <v>16</v>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B94" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="n">
-        <v>378</v>
+        <v>123</v>
       </c>
       <c r="F94" t="n">
         <v>16</v>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B95" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="F95" t="n">
         <v>16</v>
@@ -2530,10 +2530,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B96" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="F96" t="n">
         <v>16</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B97" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2566,18 +2566,18 @@
         <v>1</v>
       </c>
       <c r="E97" t="n">
-        <v>394</v>
+        <v>123</v>
       </c>
       <c r="F97" t="n">
-        <v>255</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2588,18 +2588,18 @@
         <v>1</v>
       </c>
       <c r="E98" t="n">
-        <v>542</v>
+        <v>229</v>
       </c>
       <c r="F98" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B99" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2610,18 +2610,18 @@
         <v>1</v>
       </c>
       <c r="E99" t="n">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="F99" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B100" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2632,18 +2632,18 @@
         <v>1</v>
       </c>
       <c r="E100" t="n">
-        <v>637</v>
+        <v>159</v>
       </c>
       <c r="F100" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B101" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2654,18 +2654,18 @@
         <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>395</v>
+        <v>160</v>
       </c>
       <c r="F101" t="n">
-        <v>256</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B102" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="F102" t="n">
         <v>16</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B103" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="E103" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="F103" t="n">
         <v>16</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B104" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2720,18 +2720,18 @@
         <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>637</v>
+        <v>160</v>
       </c>
       <c r="F104" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B105" t="n">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>379</v>
+        <v>159</v>
       </c>
       <c r="F105" t="n">
         <v>16</v>
@@ -2750,10 +2750,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B106" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2764,18 +2764,18 @@
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>379</v>
+        <v>123</v>
       </c>
       <c r="F106" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B107" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2786,18 +2786,18 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>143</v>
+        <v>229</v>
       </c>
       <c r="F107" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B108" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>379</v>
+        <v>90</v>
       </c>
       <c r="F108" t="n">
         <v>16</v>
@@ -2816,10 +2816,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B109" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F109" t="n">
         <v>16</v>
@@ -2838,10 +2838,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B110" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>68</v>
+        <v>160</v>
       </c>
       <c r="F110" t="n">
         <v>16</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B111" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2874,18 +2874,18 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>395</v>
+        <v>123</v>
       </c>
       <c r="F111" t="n">
-        <v>255</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B112" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="F112" t="n">
         <v>16</v>
@@ -2904,10 +2904,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B113" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2918,18 +2918,18 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>664</v>
+        <v>160</v>
       </c>
       <c r="F113" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B114" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2940,18 +2940,18 @@
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>229</v>
+        <v>111</v>
       </c>
       <c r="F114" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B115" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2962,18 +2962,18 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="F115" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B116" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="F116" t="n">
         <v>16</v>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B117" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -3006,18 +3006,18 @@
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="F117" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B118" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -3028,18 +3028,18 @@
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="F118" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B119" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="F119" t="n">
         <v>16</v>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B120" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>171</v>
+        <v>388</v>
       </c>
       <c r="F120" t="n">
         <v>19</v>
@@ -3080,10 +3080,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B121" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="F121" t="n">
         <v>19</v>
@@ -3102,10 +3102,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B122" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="F122" t="n">
         <v>19</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B123" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>171</v>
+        <v>50</v>
       </c>
       <c r="F123" t="n">
         <v>19</v>
@@ -3146,10 +3146,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B124" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>159</v>
+        <v>388</v>
       </c>
       <c r="F124" t="n">
         <v>19</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B125" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>160</v>
+        <v>109</v>
       </c>
       <c r="F125" t="n">
         <v>19</v>
@@ -3190,10 +3190,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B126" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -3204,18 +3204,18 @@
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="F126" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B127" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -3226,18 +3226,18 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="F127" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B128" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3248,18 +3248,18 @@
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="F128" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B129" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3270,18 +3270,18 @@
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="F129" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B130" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -3292,18 +3292,18 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="F130" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B131" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3314,18 +3314,18 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B132" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3336,18 +3336,18 @@
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="F132" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B133" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3358,18 +3358,18 @@
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>229</v>
+        <v>127</v>
       </c>
       <c r="F133" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B134" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3380,18 +3380,18 @@
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F134" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B135" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3402,18 +3402,18 @@
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="F135" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B136" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>159</v>
+        <v>248</v>
       </c>
       <c r="F136" t="n">
         <v>16</v>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B137" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>172</v>
+        <v>250</v>
       </c>
       <c r="F137" t="n">
         <v>16</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B138" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="F138" t="n">
         <v>16</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B139" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3490,18 +3490,18 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>544</v>
+        <v>250</v>
       </c>
       <c r="F139" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B140" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="F140" t="n">
         <v>16</v>
@@ -3520,10 +3520,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B141" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="F141" t="n">
         <v>16</v>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B142" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="F142" t="n">
         <v>16</v>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B143" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="F143" t="n">
         <v>16</v>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B144" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3600,40 +3600,40 @@
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>111</v>
+        <v>651</v>
       </c>
       <c r="F144" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
+        <v>31</v>
+      </c>
+      <c r="B145" t="n">
+        <v>32</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>544</v>
+      </c>
+      <c r="F145" t="n">
         <v>38</v>
-      </c>
-      <c r="B145" t="n">
-        <v>39</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>172</v>
-      </c>
-      <c r="F145" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B146" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F146" t="n">
         <v>16</v>
@@ -3652,10 +3652,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B147" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3666,18 +3666,18 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>172</v>
+        <v>622</v>
       </c>
       <c r="F147" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B148" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F148" t="n">
         <v>16</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B149" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3710,18 +3710,18 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>229</v>
+        <v>622</v>
       </c>
       <c r="F149" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B150" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F150" t="n">
         <v>16</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B151" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3754,18 +3754,18 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>149</v>
+        <v>652</v>
       </c>
       <c r="F151" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B152" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B153" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B154" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3820,18 +3820,18 @@
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F154" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B155" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3842,18 +3842,18 @@
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>146</v>
+        <v>668</v>
       </c>
       <c r="F155" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B156" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>149</v>
+        <v>378</v>
       </c>
       <c r="F156" t="n">
         <v>16</v>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B157" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3886,18 +3886,18 @@
         <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>143</v>
+        <v>378</v>
       </c>
       <c r="F157" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B158" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3908,18 +3908,18 @@
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>543</v>
+        <v>146</v>
       </c>
       <c r="F158" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B159" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>68</v>
+        <v>378</v>
       </c>
       <c r="F159" t="n">
         <v>16</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B160" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3952,18 +3952,18 @@
         <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>394</v>
+        <v>143</v>
       </c>
       <c r="F160" t="n">
-        <v>255</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B161" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="F161" t="n">
         <v>16</v>
@@ -3982,10 +3982,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B162" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3999,15 +3999,15 @@
         <v>394</v>
       </c>
       <c r="F162" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B163" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -4018,18 +4018,18 @@
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>68</v>
+        <v>542</v>
       </c>
       <c r="F163" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B164" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -4040,18 +4040,18 @@
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F164" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B165" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -4062,18 +4062,18 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>143</v>
+        <v>637</v>
       </c>
       <c r="F165" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B166" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -4084,18 +4084,18 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>149</v>
+        <v>395</v>
       </c>
       <c r="F166" t="n">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B167" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="F167" t="n">
         <v>16</v>
@@ -4114,10 +4114,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B168" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="F168" t="n">
         <v>16</v>
@@ -4136,10 +4136,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B169" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -4150,18 +4150,18 @@
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>394</v>
+        <v>637</v>
       </c>
       <c r="F169" t="n">
-        <v>255</v>
+        <v>20</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B170" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F170" t="n">
         <v>16</v>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B171" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F171" t="n">
         <v>20</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B172" t="n">
         <v>52</v>
@@ -4216,7 +4216,7 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>378</v>
+        <v>143</v>
       </c>
       <c r="F172" t="n">
         <v>16</v>
@@ -4224,10 +4224,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B173" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F173" t="n">
         <v>16</v>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B174" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -4260,18 +4260,18 @@
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>378</v>
+        <v>147</v>
       </c>
       <c r="F174" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B175" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>378</v>
+        <v>68</v>
       </c>
       <c r="F175" t="n">
         <v>16</v>
@@ -4290,10 +4290,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B176" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -4304,18 +4304,18 @@
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>229</v>
+        <v>395</v>
       </c>
       <c r="F176" t="n">
-        <v>19</v>
+        <v>255</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B177" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -4326,18 +4326,18 @@
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F177" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B178" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -4348,18 +4348,18 @@
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>160</v>
+        <v>664</v>
       </c>
       <c r="F178" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B179" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>229</v>
+        <v>171</v>
       </c>
       <c r="F179" t="n">
         <v>19</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B180" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -4395,15 +4395,15 @@
         <v>159</v>
       </c>
       <c r="F180" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B181" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -4417,15 +4417,15 @@
         <v>160</v>
       </c>
       <c r="F181" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B182" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -4436,18 +4436,18 @@
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="F182" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B183" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -4458,18 +4458,18 @@
         <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="F183" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="B184" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -4480,18 +4480,18 @@
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>521</v>
+        <v>160</v>
       </c>
       <c r="F184" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B185" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -4502,18 +4502,18 @@
         <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>388</v>
+        <v>148</v>
       </c>
       <c r="F185" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B186" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -4524,18 +4524,18 @@
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F186" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B187" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4546,18 +4546,18 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="F187" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B188" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -4568,18 +4568,18 @@
         <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>208</v>
+        <v>147</v>
       </c>
       <c r="F188" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B189" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -4590,18 +4590,18 @@
         <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>350</v>
+        <v>143</v>
       </c>
       <c r="F189" t="n">
-        <v>301</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B190" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4612,18 +4612,18 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>215</v>
+        <v>147</v>
       </c>
       <c r="F190" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B191" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -4634,18 +4634,18 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>115</v>
+        <v>172</v>
       </c>
       <c r="F191" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B192" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="F192" t="n">
         <v>19</v>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B193" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4678,18 +4678,18 @@
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="F193" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B194" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -4700,18 +4700,18 @@
         <v>1</v>
       </c>
       <c r="E194" t="n">
-        <v>118</v>
+        <v>544</v>
       </c>
       <c r="F194" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B195" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -4722,18 +4722,18 @@
         <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="F195" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B196" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="F196" t="n">
         <v>19</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B197" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -4766,18 +4766,18 @@
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>388</v>
+        <v>172</v>
       </c>
       <c r="F197" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B198" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -4788,15 +4788,15 @@
         <v>1</v>
       </c>
       <c r="E198" t="n">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="F198" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B199" t="n">
         <v>70</v>
@@ -4810,40 +4810,40 @@
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>109</v>
+        <v>394</v>
       </c>
       <c r="F199" t="n">
-        <v>19</v>
+        <v>255</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
+        <v>62</v>
+      </c>
+      <c r="B200" t="n">
+        <v>71</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
         <v>69</v>
       </c>
-      <c r="B200" t="n">
-        <v>70</v>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" t="n">
-        <v>71</v>
-      </c>
       <c r="F200" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B201" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -4854,18 +4854,18 @@
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="F201" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B202" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -4876,18 +4876,18 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F202" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B203" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -4898,18 +4898,18 @@
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="F203" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B204" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -4920,18 +4920,18 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="F204" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B205" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -4942,19 +4942,19 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>69</v>
+        <v>543</v>
       </c>
       <c r="F205" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
+        <v>65</v>
+      </c>
+      <c r="B206" t="n">
         <v>72</v>
       </c>
-      <c r="B206" t="n">
-        <v>75</v>
-      </c>
       <c r="C206" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -4964,19 +4964,19 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="F206" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
+        <v>65</v>
+      </c>
+      <c r="B207" t="n">
         <v>73</v>
       </c>
-      <c r="B207" t="n">
-        <v>75</v>
-      </c>
       <c r="C207" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -4986,18 +4986,18 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>127</v>
+        <v>394</v>
       </c>
       <c r="F207" t="n">
-        <v>19</v>
+        <v>255</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B208" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -5008,19 +5008,19 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="F208" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
+        <v>66</v>
+      </c>
+      <c r="B209" t="n">
         <v>74</v>
       </c>
-      <c r="B209" t="n">
-        <v>75</v>
-      </c>
       <c r="C209" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -5030,18 +5030,18 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>127</v>
+        <v>394</v>
       </c>
       <c r="F209" t="n">
-        <v>19</v>
+        <v>256</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B210" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -5052,18 +5052,18 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="F210" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B211" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -5074,32 +5074,736 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="F211" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
+        <v>67</v>
+      </c>
+      <c r="B212" t="n">
+        <v>75</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>143</v>
+      </c>
+      <c r="F212" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>68</v>
+      </c>
+      <c r="B213" t="n">
+        <v>69</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>149</v>
+      </c>
+      <c r="F213" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>68</v>
+      </c>
+      <c r="B214" t="n">
         <v>76</v>
       </c>
-      <c r="B212" t="n">
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>147</v>
+      </c>
+      <c r="F214" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>69</v>
+      </c>
+      <c r="B215" t="n">
+        <v>76</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>68</v>
+      </c>
+      <c r="F215" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>69</v>
+      </c>
+      <c r="B216" t="n">
+        <v>77</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>394</v>
+      </c>
+      <c r="F216" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>70</v>
+      </c>
+      <c r="B217" t="n">
+        <v>71</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>378</v>
+      </c>
+      <c r="F217" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>71</v>
+      </c>
+      <c r="B218" t="n">
+        <v>72</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>378</v>
+      </c>
+      <c r="F218" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>72</v>
+      </c>
+      <c r="B219" t="n">
+        <v>73</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>378</v>
+      </c>
+      <c r="F219" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>74</v>
+      </c>
+      <c r="B220" t="n">
+        <v>75</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>378</v>
+      </c>
+      <c r="F220" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>75</v>
+      </c>
+      <c r="B221" t="n">
+        <v>76</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>378</v>
+      </c>
+      <c r="F221" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>76</v>
+      </c>
+      <c r="B222" t="n">
+        <v>77</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>378</v>
+      </c>
+      <c r="F222" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
         <v>78</v>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1</v>
-      </c>
-      <c r="E212" t="n">
+      <c r="B223" t="n">
+        <v>79</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="n">
+        <v>521</v>
+      </c>
+      <c r="F223" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>78</v>
+      </c>
+      <c r="B224" t="n">
+        <v>80</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="n">
+        <v>104</v>
+      </c>
+      <c r="F224" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>79</v>
+      </c>
+      <c r="B225" t="n">
+        <v>80</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>208</v>
+      </c>
+      <c r="F225" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>79</v>
+      </c>
+      <c r="B226" t="n">
+        <v>81</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="n">
+        <v>350</v>
+      </c>
+      <c r="F226" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>79</v>
+      </c>
+      <c r="B227" t="n">
+        <v>82</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="n">
+        <v>215</v>
+      </c>
+      <c r="F227" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>79</v>
+      </c>
+      <c r="B228" t="n">
+        <v>84</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="n">
+        <v>115</v>
+      </c>
+      <c r="F228" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>79</v>
+      </c>
+      <c r="B229" t="n">
+        <v>85</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>97</v>
+      </c>
+      <c r="F229" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>79</v>
+      </c>
+      <c r="B230" t="n">
+        <v>86</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>94</v>
+      </c>
+      <c r="F230" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>80</v>
+      </c>
+      <c r="B231" t="n">
+        <v>82</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>104</v>
+      </c>
+      <c r="F231" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>81</v>
+      </c>
+      <c r="B232" t="n">
+        <v>84</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="n">
+        <v>88</v>
+      </c>
+      <c r="F232" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>81</v>
+      </c>
+      <c r="B233" t="n">
+        <v>86</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="n">
+        <v>94</v>
+      </c>
+      <c r="F233" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>82</v>
+      </c>
+      <c r="B234" t="n">
+        <v>85</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="n">
+        <v>104</v>
+      </c>
+      <c r="F234" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>83</v>
+      </c>
+      <c r="B235" t="n">
+        <v>85</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="n">
+        <v>97</v>
+      </c>
+      <c r="F235" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>84</v>
+      </c>
+      <c r="B236" t="n">
+        <v>86</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="n">
         <v>100</v>
       </c>
-      <c r="F212" t="n">
+      <c r="F236" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>22</v>
+      </c>
+      <c r="B237" t="n">
+        <v>30</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="n">
+        <v>219</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>23</v>
+      </c>
+      <c r="B238" t="n">
+        <v>31</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="n">
+        <v>218</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>24</v>
+      </c>
+      <c r="B239" t="n">
+        <v>32</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="n">
+        <v>218</v>
+      </c>
+      <c r="F239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>25</v>
+      </c>
+      <c r="B240" t="n">
+        <v>33</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="n">
+        <v>218</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>26</v>
+      </c>
+      <c r="B241" t="n">
+        <v>54</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="n">
+        <v>217</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>27</v>
+      </c>
+      <c r="B242" t="n">
+        <v>57</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="n">
+        <v>217</v>
+      </c>
+      <c r="F242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>28</v>
+      </c>
+      <c r="B243" t="n">
+        <v>58</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>217</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>29</v>
+      </c>
+      <c r="B244" t="n">
+        <v>61</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="n">
+        <v>217</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/9875.xlsx
+++ b/output/topology_excel/9875.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F244"/>
+  <dimension ref="A1:L244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,42 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
         </is>
       </c>
     </row>
@@ -481,6 +511,12 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +539,12 @@
       <c r="F3" t="n">
         <v>16</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +567,12 @@
       <c r="F4" t="n">
         <v>16</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +595,12 @@
       <c r="F5" t="n">
         <v>16</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +623,12 @@
       <c r="F6" t="n">
         <v>16</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +651,12 @@
       <c r="F7" t="n">
         <v>16</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +679,12 @@
       <c r="F8" t="n">
         <v>16</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +707,12 @@
       <c r="F9" t="n">
         <v>16</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +735,12 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +763,12 @@
       <c r="F11" t="n">
         <v>16</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +791,12 @@
       <c r="F12" t="n">
         <v>16</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +819,12 @@
       <c r="F13" t="n">
         <v>16</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +847,12 @@
       <c r="F14" t="n">
         <v>16</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +875,12 @@
       <c r="F15" t="n">
         <v>16</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +903,12 @@
       <c r="F16" t="n">
         <v>16</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +931,12 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +959,12 @@
       <c r="F18" t="n">
         <v>16</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +987,12 @@
       <c r="F19" t="n">
         <v>16</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +1015,12 @@
       <c r="F20" t="n">
         <v>16</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +1043,12 @@
       <c r="F21" t="n">
         <v>16</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +1071,12 @@
       <c r="F22" t="n">
         <v>16</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1099,12 @@
       <c r="F23" t="n">
         <v>16</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1127,12 @@
       <c r="F24" t="n">
         <v>16</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1155,12 @@
       <c r="F25" t="n">
         <v>16</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1183,12 @@
       <c r="F26" t="n">
         <v>16</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1211,12 @@
       <c r="F27" t="n">
         <v>16</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1239,12 @@
       <c r="F28" t="n">
         <v>16</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1267,12 @@
       <c r="F29" t="n">
         <v>16</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1295,12 @@
       <c r="F30" t="n">
         <v>16</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1323,12 @@
       <c r="F31" t="n">
         <v>16</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1351,12 @@
       <c r="F32" t="n">
         <v>16</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1379,12 @@
       <c r="F33" t="n">
         <v>16</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,6 +1407,12 @@
       <c r="F34" t="n">
         <v>16</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1435,12 @@
       <c r="F35" t="n">
         <v>16</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1463,12 @@
       <c r="F36" t="n">
         <v>16</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1491,12 @@
       <c r="F37" t="n">
         <v>16</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1519,12 @@
       <c r="F38" t="n">
         <v>16</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1547,12 @@
       <c r="F39" t="n">
         <v>16</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1575,12 @@
       <c r="F40" t="n">
         <v>16</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1603,12 @@
       <c r="F41" t="n">
         <v>16</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1631,12 @@
       <c r="F42" t="n">
         <v>16</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1659,12 @@
       <c r="F43" t="n">
         <v>16</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1687,12 @@
       <c r="F44" t="n">
         <v>16</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1715,12 @@
       <c r="F45" t="n">
         <v>16</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1743,12 @@
       <c r="F46" t="n">
         <v>16</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1771,12 @@
       <c r="F47" t="n">
         <v>16</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1799,12 @@
       <c r="F48" t="n">
         <v>16</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1827,12 @@
       <c r="F49" t="n">
         <v>16</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1855,12 @@
       <c r="F50" t="n">
         <v>16</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1883,12 @@
       <c r="F51" t="n">
         <v>16</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1581,6 +1911,12 @@
       <c r="F52" t="n">
         <v>16</v>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1939,12 @@
       <c r="F53" t="n">
         <v>17</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1967,12 @@
       <c r="F54" t="n">
         <v>17</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1995,12 @@
       <c r="F55" t="n">
         <v>16</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1669,6 +2023,12 @@
       <c r="F56" t="n">
         <v>16</v>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +2051,12 @@
       <c r="F57" t="n">
         <v>16</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +2079,12 @@
       <c r="F58" t="n">
         <v>19</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +2107,12 @@
       <c r="F59" t="n">
         <v>19</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1757,6 +2135,12 @@
       <c r="F60" t="n">
         <v>19</v>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1779,6 +2163,12 @@
       <c r="F61" t="n">
         <v>19</v>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1801,6 +2191,12 @@
       <c r="F62" t="n">
         <v>19</v>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1823,6 +2219,12 @@
       <c r="F63" t="n">
         <v>19</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1845,6 +2247,12 @@
       <c r="F64" t="n">
         <v>15</v>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1867,6 +2275,12 @@
       <c r="F65" t="n">
         <v>19</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2303,12 @@
       <c r="F66" t="n">
         <v>19</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2331,12 @@
       <c r="F67" t="n">
         <v>19</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2359,12 @@
       <c r="F68" t="n">
         <v>19</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2387,12 @@
       <c r="F69" t="n">
         <v>15</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1977,6 +2415,12 @@
       <c r="F70" t="n">
         <v>15</v>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1999,6 +2443,12 @@
       <c r="F71" t="n">
         <v>19</v>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2021,6 +2471,12 @@
       <c r="F72" t="n">
         <v>16</v>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2043,6 +2499,12 @@
       <c r="F73" t="n">
         <v>19</v>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2065,6 +2527,12 @@
       <c r="F74" t="n">
         <v>16</v>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2087,6 +2555,12 @@
       <c r="F75" t="n">
         <v>16</v>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2109,6 +2583,12 @@
       <c r="F76" t="n">
         <v>16</v>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2131,6 +2611,12 @@
       <c r="F77" t="n">
         <v>16</v>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2151,8 +2637,14 @@
         <v>113</v>
       </c>
       <c r="F78" t="n">
-        <v>38</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2175,6 +2667,12 @@
       <c r="F79" t="n">
         <v>16</v>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2197,6 +2695,12 @@
       <c r="F80" t="n">
         <v>16</v>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2219,6 +2723,12 @@
       <c r="F81" t="n">
         <v>16</v>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2241,6 +2751,12 @@
       <c r="F82" t="n">
         <v>16</v>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2263,6 +2779,12 @@
       <c r="F83" t="n">
         <v>19</v>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2285,6 +2807,12 @@
       <c r="F84" t="n">
         <v>16</v>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2307,6 +2835,12 @@
       <c r="F85" t="n">
         <v>16</v>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2329,6 +2863,12 @@
       <c r="F86" t="n">
         <v>16</v>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2351,6 +2891,12 @@
       <c r="F87" t="n">
         <v>16</v>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2373,6 +2919,12 @@
       <c r="F88" t="n">
         <v>16</v>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2395,6 +2947,12 @@
       <c r="F89" t="n">
         <v>16</v>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2417,6 +2975,12 @@
       <c r="F90" t="n">
         <v>19</v>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2439,6 +3003,12 @@
       <c r="F91" t="n">
         <v>16</v>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2461,6 +3031,12 @@
       <c r="F92" t="n">
         <v>16</v>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2483,6 +3059,12 @@
       <c r="F93" t="n">
         <v>16</v>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2505,6 +3087,12 @@
       <c r="F94" t="n">
         <v>16</v>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2527,6 +3115,12 @@
       <c r="F95" t="n">
         <v>16</v>
       </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2549,6 +3143,12 @@
       <c r="F96" t="n">
         <v>16</v>
       </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2571,6 +3171,12 @@
       <c r="F97" t="n">
         <v>17</v>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2593,6 +3199,12 @@
       <c r="F98" t="n">
         <v>19</v>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2615,6 +3227,12 @@
       <c r="F99" t="n">
         <v>17</v>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2637,6 +3255,12 @@
       <c r="F100" t="n">
         <v>17</v>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2659,6 +3283,12 @@
       <c r="F101" t="n">
         <v>16</v>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2681,6 +3311,12 @@
       <c r="F102" t="n">
         <v>16</v>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2703,6 +3339,12 @@
       <c r="F103" t="n">
         <v>16</v>
       </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2725,6 +3367,12 @@
       <c r="F104" t="n">
         <v>17</v>
       </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2747,6 +3395,12 @@
       <c r="F105" t="n">
         <v>16</v>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2769,6 +3423,12 @@
       <c r="F106" t="n">
         <v>16</v>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2791,6 +3451,12 @@
       <c r="F107" t="n">
         <v>19</v>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2813,6 +3479,12 @@
       <c r="F108" t="n">
         <v>16</v>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2835,6 +3507,12 @@
       <c r="F109" t="n">
         <v>16</v>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2857,6 +3535,12 @@
       <c r="F110" t="n">
         <v>16</v>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2879,6 +3563,12 @@
       <c r="F111" t="n">
         <v>16</v>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2901,6 +3591,12 @@
       <c r="F112" t="n">
         <v>16</v>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2923,6 +3619,12 @@
       <c r="F113" t="n">
         <v>16</v>
       </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2945,6 +3647,12 @@
       <c r="F114" t="n">
         <v>16</v>
       </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2965,8 +3673,14 @@
         <v>111</v>
       </c>
       <c r="F115" t="n">
-        <v>38</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2989,6 +3703,12 @@
       <c r="F116" t="n">
         <v>16</v>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3011,6 +3731,12 @@
       <c r="F117" t="n">
         <v>17</v>
       </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3031,8 +3757,14 @@
         <v>110</v>
       </c>
       <c r="F118" t="n">
-        <v>39</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3055,6 +3787,12 @@
       <c r="F119" t="n">
         <v>16</v>
       </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3069,14 +3807,24 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>388</v>
+        <v>290</v>
       </c>
       <c r="F120" t="n">
         <v>19</v>
       </c>
+      <c r="G120" t="n">
+        <v>88</v>
+      </c>
+      <c r="H120" t="n">
+        <v>19</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3099,6 +3847,12 @@
       <c r="F121" t="n">
         <v>19</v>
       </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3121,6 +3875,12 @@
       <c r="F122" t="n">
         <v>19</v>
       </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3143,6 +3903,12 @@
       <c r="F123" t="n">
         <v>19</v>
       </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3157,12 +3923,30 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E124" t="n">
-        <v>388</v>
+        <v>89</v>
       </c>
       <c r="F124" t="n">
+        <v>19</v>
+      </c>
+      <c r="G124" t="n">
+        <v>94</v>
+      </c>
+      <c r="H124" t="n">
+        <v>19</v>
+      </c>
+      <c r="I124" t="n">
+        <v>82</v>
+      </c>
+      <c r="J124" t="n">
+        <v>19</v>
+      </c>
+      <c r="K124" t="n">
+        <v>90</v>
+      </c>
+      <c r="L124" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3187,6 +3971,12 @@
       <c r="F125" t="n">
         <v>19</v>
       </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3209,6 +3999,12 @@
       <c r="F126" t="n">
         <v>19</v>
       </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3231,6 +4027,12 @@
       <c r="F127" t="n">
         <v>19</v>
       </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3253,6 +4055,12 @@
       <c r="F128" t="n">
         <v>19</v>
       </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3275,6 +4083,12 @@
       <c r="F129" t="n">
         <v>19</v>
       </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3297,6 +4111,12 @@
       <c r="F130" t="n">
         <v>19</v>
       </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3319,6 +4139,12 @@
       <c r="F131" t="n">
         <v>19</v>
       </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3341,6 +4167,12 @@
       <c r="F132" t="n">
         <v>19</v>
       </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3363,6 +4195,12 @@
       <c r="F133" t="n">
         <v>19</v>
       </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3385,6 +4223,12 @@
       <c r="F134" t="n">
         <v>19</v>
       </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3407,6 +4251,12 @@
       <c r="F135" t="n">
         <v>16</v>
       </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3429,6 +4279,12 @@
       <c r="F136" t="n">
         <v>16</v>
       </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3451,6 +4307,12 @@
       <c r="F137" t="n">
         <v>16</v>
       </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3473,6 +4335,12 @@
       <c r="F138" t="n">
         <v>16</v>
       </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3495,6 +4363,12 @@
       <c r="F139" t="n">
         <v>16</v>
       </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3517,6 +4391,12 @@
       <c r="F140" t="n">
         <v>16</v>
       </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3539,6 +4419,12 @@
       <c r="F141" t="n">
         <v>16</v>
       </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3561,6 +4447,12 @@
       <c r="F142" t="n">
         <v>16</v>
       </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3583,6 +4475,12 @@
       <c r="F143" t="n">
         <v>16</v>
       </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3597,14 +4495,24 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
-        <v>651</v>
+        <v>242</v>
       </c>
       <c r="F144" t="n">
         <v>19</v>
       </c>
+      <c r="G144" t="n">
+        <v>401</v>
+      </c>
+      <c r="H144" t="n">
+        <v>19</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3625,8 +4533,14 @@
         <v>544</v>
       </c>
       <c r="F145" t="n">
-        <v>38</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3649,6 +4563,12 @@
       <c r="F146" t="n">
         <v>16</v>
       </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3663,14 +4583,24 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>622</v>
+        <v>402</v>
       </c>
       <c r="F147" t="n">
         <v>19</v>
       </c>
+      <c r="G147" t="n">
+        <v>212</v>
+      </c>
+      <c r="H147" t="n">
+        <v>19</v>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3693,6 +4623,12 @@
       <c r="F148" t="n">
         <v>16</v>
       </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3707,14 +4643,24 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
-        <v>622</v>
+        <v>213</v>
       </c>
       <c r="F149" t="n">
         <v>19</v>
       </c>
+      <c r="G149" t="n">
+        <v>400</v>
+      </c>
+      <c r="H149" t="n">
+        <v>19</v>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3737,6 +4683,12 @@
       <c r="F150" t="n">
         <v>16</v>
       </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3751,14 +4703,24 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>652</v>
+        <v>401</v>
       </c>
       <c r="F151" t="n">
         <v>19</v>
       </c>
+      <c r="G151" t="n">
+        <v>242</v>
+      </c>
+      <c r="H151" t="n">
+        <v>19</v>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3773,14 +4735,24 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="F152" t="n">
-        <v>255</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G152" t="n">
+        <v>239</v>
+      </c>
+      <c r="H152" t="n">
+        <v>16</v>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3803,6 +4775,12 @@
       <c r="F153" t="n">
         <v>16</v>
       </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3825,6 +4803,12 @@
       <c r="F154" t="n">
         <v>16</v>
       </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -3847,6 +4831,12 @@
       <c r="F155" t="n">
         <v>20</v>
       </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -3869,6 +4859,12 @@
       <c r="F156" t="n">
         <v>16</v>
       </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3891,6 +4887,12 @@
       <c r="F157" t="n">
         <v>20</v>
       </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3913,6 +4915,12 @@
       <c r="F158" t="n">
         <v>16</v>
       </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3935,6 +4943,12 @@
       <c r="F159" t="n">
         <v>16</v>
       </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3957,6 +4971,12 @@
       <c r="F160" t="n">
         <v>16</v>
       </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3979,6 +4999,12 @@
       <c r="F161" t="n">
         <v>16</v>
       </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3993,14 +5019,24 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" t="n">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="F162" t="n">
-        <v>255</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G162" t="n">
+        <v>239</v>
+      </c>
+      <c r="H162" t="n">
+        <v>16</v>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4023,6 +5059,12 @@
       <c r="F163" t="n">
         <v>20</v>
       </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4045,6 +5087,12 @@
       <c r="F164" t="n">
         <v>16</v>
       </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4067,6 +5115,12 @@
       <c r="F165" t="n">
         <v>20</v>
       </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4081,14 +5135,24 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" t="n">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="F166" t="n">
-        <v>256</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G166" t="n">
+        <v>240</v>
+      </c>
+      <c r="H166" t="n">
+        <v>16</v>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4111,6 +5175,12 @@
       <c r="F167" t="n">
         <v>16</v>
       </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4133,6 +5203,12 @@
       <c r="F168" t="n">
         <v>16</v>
       </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4155,6 +5231,12 @@
       <c r="F169" t="n">
         <v>20</v>
       </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4177,6 +5259,12 @@
       <c r="F170" t="n">
         <v>16</v>
       </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4199,6 +5287,12 @@
       <c r="F171" t="n">
         <v>20</v>
       </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4221,6 +5315,12 @@
       <c r="F172" t="n">
         <v>16</v>
       </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4243,6 +5343,12 @@
       <c r="F173" t="n">
         <v>16</v>
       </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4265,6 +5371,12 @@
       <c r="F174" t="n">
         <v>16</v>
       </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4287,6 +5399,12 @@
       <c r="F175" t="n">
         <v>16</v>
       </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4301,14 +5419,24 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="F176" t="n">
-        <v>255</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G176" t="n">
+        <v>239</v>
+      </c>
+      <c r="H176" t="n">
+        <v>16</v>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4331,6 +5459,12 @@
       <c r="F177" t="n">
         <v>16</v>
       </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4353,6 +5487,12 @@
       <c r="F178" t="n">
         <v>20</v>
       </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4375,6 +5515,12 @@
       <c r="F179" t="n">
         <v>19</v>
       </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4397,6 +5543,12 @@
       <c r="F180" t="n">
         <v>19</v>
       </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4419,6 +5571,12 @@
       <c r="F181" t="n">
         <v>19</v>
       </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4441,6 +5599,12 @@
       <c r="F182" t="n">
         <v>19</v>
       </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4463,6 +5627,12 @@
       <c r="F183" t="n">
         <v>19</v>
       </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4485,6 +5655,12 @@
       <c r="F184" t="n">
         <v>19</v>
       </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4507,6 +5683,12 @@
       <c r="F185" t="n">
         <v>20</v>
       </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4529,6 +5711,12 @@
       <c r="F186" t="n">
         <v>20</v>
       </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4551,6 +5739,12 @@
       <c r="F187" t="n">
         <v>20</v>
       </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4573,6 +5767,12 @@
       <c r="F188" t="n">
         <v>20</v>
       </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4595,6 +5795,12 @@
       <c r="F189" t="n">
         <v>20</v>
       </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4617,6 +5823,12 @@
       <c r="F190" t="n">
         <v>20</v>
       </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4639,6 +5851,12 @@
       <c r="F191" t="n">
         <v>17</v>
       </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4661,6 +5879,12 @@
       <c r="F192" t="n">
         <v>19</v>
       </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4683,6 +5907,12 @@
       <c r="F193" t="n">
         <v>16</v>
       </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4703,8 +5933,14 @@
         <v>544</v>
       </c>
       <c r="F194" t="n">
-        <v>38</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4727,6 +5963,12 @@
       <c r="F195" t="n">
         <v>16</v>
       </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4749,6 +5991,12 @@
       <c r="F196" t="n">
         <v>19</v>
       </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4771,6 +6019,12 @@
       <c r="F197" t="n">
         <v>16</v>
       </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4793,6 +6047,12 @@
       <c r="F198" t="n">
         <v>16</v>
       </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4807,14 +6067,24 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E199" t="n">
-        <v>394</v>
+        <v>239</v>
       </c>
       <c r="F199" t="n">
-        <v>255</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G199" t="n">
+        <v>378</v>
+      </c>
+      <c r="H199" t="n">
+        <v>16</v>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4837,6 +6107,12 @@
       <c r="F200" t="n">
         <v>16</v>
       </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4859,6 +6135,12 @@
       <c r="F201" t="n">
         <v>20</v>
       </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4881,6 +6163,12 @@
       <c r="F202" t="n">
         <v>16</v>
       </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4903,6 +6191,12 @@
       <c r="F203" t="n">
         <v>16</v>
       </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4925,6 +6219,12 @@
       <c r="F204" t="n">
         <v>16</v>
       </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4947,6 +6247,12 @@
       <c r="F205" t="n">
         <v>20</v>
       </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4969,6 +6275,12 @@
       <c r="F206" t="n">
         <v>16</v>
       </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4983,14 +6295,24 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" t="n">
-        <v>394</v>
+        <v>239</v>
       </c>
       <c r="F207" t="n">
-        <v>255</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G207" t="n">
+        <v>378</v>
+      </c>
+      <c r="H207" t="n">
+        <v>16</v>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5013,6 +6335,12 @@
       <c r="F208" t="n">
         <v>16</v>
       </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5027,14 +6355,24 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" t="n">
-        <v>394</v>
+        <v>240</v>
       </c>
       <c r="F209" t="n">
-        <v>256</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G209" t="n">
+        <v>378</v>
+      </c>
+      <c r="H209" t="n">
+        <v>16</v>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5057,6 +6395,12 @@
       <c r="F210" t="n">
         <v>16</v>
       </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5079,6 +6423,12 @@
       <c r="F211" t="n">
         <v>20</v>
       </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5101,6 +6451,12 @@
       <c r="F212" t="n">
         <v>16</v>
       </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5123,6 +6479,12 @@
       <c r="F213" t="n">
         <v>16</v>
       </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -5145,6 +6507,12 @@
       <c r="F214" t="n">
         <v>16</v>
       </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -5167,6 +6535,12 @@
       <c r="F215" t="n">
         <v>16</v>
       </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -5181,14 +6555,24 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" t="n">
-        <v>394</v>
+        <v>239</v>
       </c>
       <c r="F216" t="n">
-        <v>255</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G216" t="n">
+        <v>378</v>
+      </c>
+      <c r="H216" t="n">
+        <v>16</v>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5211,6 +6595,12 @@
       <c r="F217" t="n">
         <v>16</v>
       </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -5233,6 +6623,12 @@
       <c r="F218" t="n">
         <v>20</v>
       </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5255,6 +6651,12 @@
       <c r="F219" t="n">
         <v>16</v>
       </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5277,6 +6679,12 @@
       <c r="F220" t="n">
         <v>16</v>
       </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5299,6 +6707,12 @@
       <c r="F221" t="n">
         <v>20</v>
       </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5321,6 +6735,12 @@
       <c r="F222" t="n">
         <v>16</v>
       </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5335,14 +6755,24 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" t="n">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="F223" t="n">
-        <v>180</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G223" t="n">
+        <v>161</v>
+      </c>
+      <c r="H223" t="n">
+        <v>19</v>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5365,6 +6795,12 @@
       <c r="F224" t="n">
         <v>19</v>
       </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -5387,6 +6823,12 @@
       <c r="F225" t="n">
         <v>19</v>
       </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -5401,14 +6843,28 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E226" t="n">
-        <v>350</v>
+        <v>271</v>
       </c>
       <c r="F226" t="n">
-        <v>301</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G226" t="n">
+        <v>123</v>
+      </c>
+      <c r="H226" t="n">
+        <v>15</v>
+      </c>
+      <c r="I226" t="n">
+        <v>335</v>
+      </c>
+      <c r="J226" t="n">
+        <v>15</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -5431,6 +6887,12 @@
       <c r="F227" t="n">
         <v>19</v>
       </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -5445,14 +6907,24 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="F228" t="n">
-        <v>102</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G228" t="n">
+        <v>89</v>
+      </c>
+      <c r="H228" t="n">
+        <v>15</v>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -5475,6 +6947,12 @@
       <c r="F229" t="n">
         <v>19</v>
       </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -5497,6 +6975,12 @@
       <c r="F230" t="n">
         <v>15</v>
       </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -5519,6 +7003,12 @@
       <c r="F231" t="n">
         <v>19</v>
       </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -5541,6 +7031,12 @@
       <c r="F232" t="n">
         <v>15</v>
       </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -5563,6 +7059,12 @@
       <c r="F233" t="n">
         <v>15</v>
       </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -5585,6 +7087,12 @@
       <c r="F234" t="n">
         <v>19</v>
       </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -5607,6 +7115,12 @@
       <c r="F235" t="n">
         <v>19</v>
       </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -5629,6 +7143,12 @@
       <c r="F236" t="n">
         <v>15</v>
       </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -5651,6 +7171,12 @@
       <c r="F237" t="n">
         <v>1</v>
       </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -5673,6 +7199,12 @@
       <c r="F238" t="n">
         <v>1</v>
       </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -5695,6 +7227,12 @@
       <c r="F239" t="n">
         <v>1</v>
       </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -5717,6 +7255,12 @@
       <c r="F240" t="n">
         <v>1</v>
       </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -5739,6 +7283,12 @@
       <c r="F241" t="n">
         <v>1</v>
       </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -5761,6 +7311,12 @@
       <c r="F242" t="n">
         <v>1</v>
       </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -5783,6 +7339,12 @@
       <c r="F243" t="n">
         <v>1</v>
       </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -5805,6 +7367,12 @@
       <c r="F244" t="n">
         <v>1</v>
       </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
